--- a/output/full_scan/batch_seq1_2026-06-11.xlsx
+++ b/output/full_scan/batch_seq1_2026-06-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O135"/>
+  <dimension ref="A1:O138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>1438</v>
+        <v>1210</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>735</v>
+        <v>963.3065255495088</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>24.05</v>
+        <v>55.7</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,49 +552,49 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>66.90497844161008</v>
+        <v>70.0958097842675</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>32.47884515656527</v>
+        <v>24.50525878642429</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>5.667226653822207</v>
+        <v>1.330652554950877</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.5606700440716467</v>
+        <v>0.3618443887826622</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>1210</v>
+        <v>1438</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>733.2314256292772</v>
+        <v>935</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>55.7</v>
+        <v>24.05</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>70.09580976344878</v>
+        <v>66.90497843051233</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>24.50525878642429</v>
+        <v>32.47884523536054</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.323142562927718</v>
+        <v>5.704054404321148</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.3618443887826622</v>
+        <v>0.5606700441288858</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1444</v>
+        <v>1307</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>704.2172133964683</v>
+        <v>924.8194708287108</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7.05</v>
+        <v>35.2</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>61.68521044861453</v>
+        <v>74.95280275598341</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>34.72500417847572</v>
+        <v>24.23365702257069</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.921721339646832</v>
+        <v>0.981947082871081</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.0714037490472418</v>
+        <v>0.3734813931138458</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1532</v>
+        <v>1444</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>702.6453511624691</v>
+        <v>914.281091559928</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>23.05</v>
+        <v>7.05</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>73.00110368351862</v>
+        <v>61.68521040216849</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>32.44106811912557</v>
+        <v>34.72500418496053</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.7645351162469016</v>
+        <v>0.9281091559927986</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2305360621108922</v>
+        <v>0.0714037490434256</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1514</v>
+        <v>1532</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>659.791609717187</v>
+        <v>852.695364697779</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>118</v>
+        <v>23.05</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>45.25733319885198</v>
+        <v>73.00110339000312</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>30.25948643869461</v>
+        <v>32.44106816033047</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.4791609717187082</v>
+        <v>0.7695364697778985</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-1.29826164297132</v>
+        <v>0.230536062091813</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1203</v>
+        <v>1319</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>味王</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>657.8469653910538</v>
+        <v>843.666584017022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>42.75</v>
+        <v>102</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>50.65989172899017</v>
+        <v>67.13788926011016</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>23.85323955540914</v>
+        <v>32.44271410827638</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.284696539105384</v>
+        <v>1.36665840170221</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.1353767303076842</v>
+        <v>1.85419395151971</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1533</v>
+        <v>1216</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>653.7194061948705</v>
+        <v>838.2995416636643</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>38.1</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>55.26926264517711</v>
+        <v>62.52297321653092</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>54.57279829358925</v>
+        <v>16.38976867415339</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.3719406194870501</v>
+        <v>0.829954166366426</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.3125376006999047</v>
+        <v>0.2460468841201276</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1342</v>
+        <v>1423</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>648.3129029455023</v>
+        <v>833.4327162494637</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>107</v>
+        <v>44.4</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>67.84038850481484</v>
+        <v>71.82385511880551</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>30.76609000837411</v>
+        <v>28.92661426340433</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.33129029455023</v>
+        <v>0.8432716249463714</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.657053813526309</v>
+        <v>0.22654918753639</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1423</v>
+        <v>1203</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>633.3889459504514</v>
+        <v>828.6417466676745</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>44.4</v>
+        <v>42.75</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>71.82385518128083</v>
+        <v>50.65989172899017</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>28.92661451284783</v>
+        <v>23.85323958801148</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.8388945950451444</v>
+        <v>1.364174666767456</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2265491874696098</v>
+        <v>-0.1353767303458392</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1303</v>
+        <v>1342</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>627.3390760433977</v>
+        <v>818.5584334246652</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>107</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>51.6135522451833</v>
+        <v>67.84038844909597</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>21.99410892537624</v>
+        <v>30.76609005944044</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.7339076043397703</v>
+        <v>1.355843342466512</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.5718860086366124</v>
+        <v>1.657053813373673</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>台翰</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>625.6616311009266</v>
+        <v>790.700272834119</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>14.25</v>
+        <v>44.3</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>59.17848247598905</v>
+        <v>60.3848992265601</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>20.46797672219122</v>
+        <v>27.32912150887644</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.066163110092661</v>
+        <v>0.5700272834118979</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.09629167751828881</v>
+        <v>0.0881586351093224</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1513</v>
+        <v>1446</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>618.4585764044457</v>
+        <v>775.2941310492475</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>164</v>
+        <v>16.8</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>50.19199054643372</v>
+        <v>65.12986099025127</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>27.17430455919888</v>
+        <v>25.40846891643726</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.3458576404445725</v>
+        <v>1.029413104924755</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.6103508740624441</v>
+        <v>0.1156476788955679</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1307</v>
+        <v>1336</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>台翰</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>609.7597542244572</v>
+        <v>765.6616311009266</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>35.2</v>
+        <v>14.25</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>74.95280303848563</v>
+        <v>59.17848219882627</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>24.23365700739803</v>
+        <v>20.46797672372708</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.975975422445717</v>
+        <v>1.066163110092661</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.3734813930184436</v>
+        <v>0.0962916775659874</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1216</v>
+        <v>1455</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>598.2025788297543</v>
+        <v>761.5815561589685</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>75.59999999999999</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>62.52297317800648</v>
+        <v>72.1553512248633</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>16.38976866209891</v>
+        <v>38.45029960883812</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.8202578829754337</v>
+        <v>1.158155615896856</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.2460468842536828</v>
+        <v>0.1560144266167885</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1447</v>
+        <v>1531</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>力鵬</t>
+          <t>高林股</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>597.0351841890174</v>
+        <v>759.4382117761849</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>6.22</v>
+        <v>12.95</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>54.8453287812522</v>
+        <v>57.29069152351183</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>40.52526249195541</v>
+        <v>20.35106092054583</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.7035184189017345</v>
+        <v>0.9438211776184851</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.008442136288176199</v>
+        <v>0.0825259942854899</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1530</v>
+        <v>1563</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>巧新</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>595.1049263883049</v>
+        <v>752.2888974724275</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>30.35</v>
+        <v>60</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>49.40137053438515</v>
+        <v>58.70442721114053</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>39.28792900809602</v>
+        <v>51.05518970227242</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.5104926388304882</v>
+        <v>0.2288897472427465</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.2897388110467864</v>
+        <v>-0.4618501204632217</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1339</v>
+        <v>1227</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>590.6316056500179</v>
+        <v>736.5210504067446</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>44.3</v>
+        <v>28.85</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>60.38489933277637</v>
+        <v>53.86153025081335</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>27.32912150401639</v>
+        <v>20.3942153300423</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.5631605650017965</v>
+        <v>1.152105040674461</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.0881586352047203</v>
+        <v>0.1069690830976335</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1531</v>
+        <v>1236</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>高林股</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>589.3660192003393</v>
+        <v>729.9138232891103</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>12.95</v>
+        <v>25.65</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>57.29069166167625</v>
+        <v>61.83218877577059</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>20.35106082338323</v>
+        <v>16.29380574627918</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.9366019200339361</v>
+        <v>0.491382328911022</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.0825259942473298</v>
+        <v>0.2068456716081972</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1560</v>
+        <v>1525</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>江申</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>580.209568596905</v>
+        <v>709.5431008836996</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>628</v>
+        <v>65.7</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>45.89935180651221</v>
+        <v>50.56226132810986</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>29.25591495398353</v>
+        <v>28.74153268010181</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.020956859690501</v>
+        <v>0.4543100883699546</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-16.33365797440062</v>
+        <v>-0.2725820644260528</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1446</v>
+        <v>1568</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>575.2409990249715</v>
+        <v>701.9076807469338</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>16.8</v>
+        <v>38</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>65.12986119366647</v>
+        <v>52.76301533081567</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>25.40846892540472</v>
+        <v>49.83556012684097</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.024099902497155</v>
+        <v>0.1907680746933822</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.1156476789337278</v>
+        <v>-0.6371971302223032</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1503</v>
+        <v>1443</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>564.7707041050636</v>
+        <v>693.5821648977119</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>215</v>
+        <v>26.45</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>50.06895430137289</v>
+        <v>58.10701326897193</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>26.61447812048452</v>
+        <v>13.60859388361744</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.4770704105063574</v>
+        <v>0.8582164897711928</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.5787878603467433</v>
+        <v>0.0040707654788659</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1455</v>
+        <v>1533</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>561.5246771561613</v>
+        <v>683.8752573225696</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>9.859999999999999</v>
+        <v>38.1</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>72.15535128989089</v>
+        <v>55.26926259697072</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>38.4502995242691</v>
+        <v>54.57279830717829</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.152467715616126</v>
+        <v>0.3875257322569594</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.1560144265919848</v>
+        <v>-0.3125376007571432</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1525</v>
+        <v>1303</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>江申</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>559.4867429940828</v>
+        <v>682.3821319201143</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>65.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,49 +1718,49 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>50.56226133651602</v>
+        <v>51.61355223808317</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>28.74153261276233</v>
+        <v>21.99410886265558</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.4486742994082777</v>
+        <v>0.7382131920114312</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.2725820643688097</v>
+        <v>-0.5718860086556985</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1236</v>
+        <v>1409</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>559.3887025044862</v>
+        <v>675.8411789317538</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>25.65</v>
+        <v>24.65</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>61.83218868962945</v>
+        <v>61.3039322593841</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>16.29380571773653</v>
+        <v>41.13599435526688</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4388702504486229</v>
+        <v>0.5841178931753765</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.206845671627276</v>
+        <v>0.1604092938906349</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1524</v>
+        <v>1437</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>542.7581113918753</v>
+        <v>646.1318685908816</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>29.75</v>
+        <v>29.15</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>46.17340249474785</v>
+        <v>55.18528165626615</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>21.4937421058402</v>
+        <v>27.79078431237902</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.2758111391875316</v>
+        <v>0.6131868590881561</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.222402981439583</v>
+        <v>0.1263892463294297</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1443</v>
+        <v>1530</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>亞崴</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>523.5214495932586</v>
+        <v>645.2760682228733</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>26.45</v>
+        <v>30.35</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>58.10701326382507</v>
+        <v>49.40137036907856</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>13.60859385797078</v>
+        <v>39.2879290261378</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.8521449593258587</v>
+        <v>0.527606822287328</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.0040707654788659</v>
+        <v>-0.2897388108369121</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1319</v>
+        <v>1402</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>518.5302144516052</v>
+        <v>640.1610490471567</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>102</v>
+        <v>27.4</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,49 +1930,49 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>67.13788927203258</v>
+        <v>55.52563498060286</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>32.44271411473388</v>
+        <v>18.61263235562054</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.353021445160509</v>
+        <v>0.5161049047156712</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1.85419395151971</v>
+        <v>0.1848837166372769</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1477</v>
+        <v>1414</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>506.7206147702397</v>
+        <v>628.6408012317709</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>225</v>
+        <v>16.75</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>52.42537121831214</v>
+        <v>57.52079614092146</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>22.64391565675309</v>
+        <v>30.01209677393267</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.6720614770239698</v>
+        <v>0.3640801231770906</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>1.051410674372144</v>
+        <v>0.2791628867462575</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1522</v>
+        <v>1321</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>504.663783366254</v>
+        <v>621.0651793122522</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>47.27659392790448</v>
+        <v>61.66928740275154</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>21.65021165133883</v>
+        <v>43.03774487106448</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.4663783366253992</v>
+        <v>1.106517931225224</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0266910574951763</v>
+        <v>0.336893304115838</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1467</v>
+        <v>1432</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>498.3744176604664</v>
+        <v>618.7459065692992</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>7.55</v>
+        <v>17.2</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>56.77455260373363</v>
+        <v>58.80003269835749</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>31.25884653295243</v>
+        <v>24.28996837135435</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.3374417660466333</v>
+        <v>0.8745906569299217</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.0535529452633621</v>
+        <v>0.103699938222252</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1301</v>
+        <v>1477</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>495.3961046162504</v>
+        <v>616.8630114110219</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>43.8</v>
+        <v>225</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,49 +2142,49 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>37.02724691772845</v>
+        <v>52.42537110476061</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>22.45878043487991</v>
+        <v>22.64391569500292</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.039610461625036</v>
+        <v>0.6863011411021903</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.3196710935716655</v>
+        <v>1.051410673036624</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1326</v>
+        <v>1234</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>黑松</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>484.9473027992179</v>
+        <v>611.9182579058643</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>46.25</v>
+        <v>35.2</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>43.32272500694859</v>
+        <v>57.76457939072906</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>23.71817634551993</v>
+        <v>19.00320209393898</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.4947302799217932</v>
+        <v>1.19182579058643</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.347550786726078</v>
+        <v>0.1311432493684987</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1218</v>
+        <v>1470</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>大統新創</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>482.2652904832945</v>
+        <v>611.6738375388502</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>19.2</v>
+        <v>22.7</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>54.84792786437915</v>
+        <v>53.39648948642267</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>22.55528167229498</v>
+        <v>2.887508895963617</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>2.726529048329445</v>
+        <v>0.1673837538850149</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.0529333344911499</v>
+        <v>0.0184093528606019</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1341</v>
+        <v>1104</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>環泥</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>481.9949636261891</v>
+        <v>606.2981213563953</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>62.1</v>
+        <v>29</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>52.00754723192875</v>
+        <v>61.73700056248686</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>13.71275840644644</v>
+        <v>33.98055067326883</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.6994963626189143</v>
+        <v>1.12981213563953</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.043829275181922</v>
+        <v>0.1839319590695775</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1314</v>
+        <v>1449</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>佳和</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>470.050205046098</v>
+        <v>605.2020028139743</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>7.76</v>
+        <v>14.25</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>55.68662181536837</v>
+        <v>54.54497648318841</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>14.48892080658208</v>
+        <v>22.6674520519248</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.5050205046098017</v>
+        <v>1.02020028139743</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.0727953790727397</v>
+        <v>0.2291860643935573</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1227</v>
+        <v>1514</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>466.4199851261245</v>
+        <v>604.9094642361309</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>28.85</v>
+        <v>118</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>53.86153023049766</v>
+        <v>45.25733317166092</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>20.39421521312696</v>
+        <v>30.25948643869461</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.141998512612448</v>
+        <v>0.4909464236130954</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.1069690831262524</v>
+        <v>-1.298261643085791</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1456</v>
+        <v>1101</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>466.3739491069654</v>
+        <v>604.6324887145717</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>13.95</v>
+        <v>24.25</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,49 +2460,49 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>56.36352640476386</v>
+        <v>49.09168121469888</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>16.39168881542418</v>
+        <v>11.72166576291005</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.137394910696541</v>
+        <v>0.9632488714571642</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M38" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.1434806758901468</v>
+        <v>-0.0161292669623804</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1104</v>
+        <v>1218</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>466.2202804843558</v>
+        <v>602.4760620719335</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>29</v>
+        <v>19.2</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>61.73700077690444</v>
+        <v>54.84792777566086</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>33.98055062242556</v>
+        <v>22.55528179753858</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.122028048435577</v>
+        <v>2.747606207193346</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.183931959012342</v>
+        <v>0.0529333345483891</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1416</v>
+        <v>1434</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>462.4473375184724</v>
+        <v>599.9795423220013</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>11.05</v>
+        <v>16.35</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>42.11014231583206</v>
+        <v>57.60230613837168</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>32.21203678124927</v>
+        <v>25.7891360523426</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.7447337518472432</v>
+        <v>0.4979542322001342</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.0227416484735684</v>
+        <v>0.1347662508627662</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1321</v>
+        <v>1513</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>461.0264113612416</v>
+        <v>598.5503914094909</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>31</v>
+        <v>164</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,49 +2619,49 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>61.66928749525843</v>
+        <v>50.19199048467812</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>43.03774472723747</v>
+        <v>27.17430456470775</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.102641136124154</v>
+        <v>0.3550391409490868</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.3368933040395206</v>
+        <v>-0.6103508739670485</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1402</v>
+        <v>1467</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>460.153629104056</v>
+        <v>598.4489393497777</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>27.4</v>
+        <v>7.55</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>55.52563501509877</v>
+        <v>56.77455261860545</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>18.61263234673139</v>
+        <v>31.25884657158782</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.5153629104055998</v>
+        <v>0.3448939349777622</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.1848837166658947</v>
+        <v>0.0535529452557313</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1434</v>
+        <v>1232</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>福懋</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>459.9435522096893</v>
+        <v>596.8900833477286</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>16.35</v>
+        <v>149.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>57.60230617549977</v>
+        <v>56.93001130118232</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>25.78913611074839</v>
+        <v>13.78564221605782</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.4943552209689285</v>
+        <v>1.189008334772861</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.1347662508532296</v>
+        <v>0.2202246035267154</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1414</v>
+        <v>1456</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>458.5938271118681</v>
+        <v>596.4983016129592</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>16.75</v>
+        <v>13.95</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>57.52079617729547</v>
+        <v>56.3635263876427</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>30.01209673498521</v>
+        <v>16.39168881542418</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.3593827111868033</v>
+        <v>1.149830161295919</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.2791628867135589</v>
+        <v>0.143480675909226</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1232</v>
+        <v>1313</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>446.3215413360566</v>
+        <v>590.5308803174088</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>149.5</v>
+        <v>11.05</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>56.93001107337376</v>
+        <v>50.03708731946692</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>13.7856421673857</v>
+        <v>17.7645641484426</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.132154133605662</v>
+        <v>0.5530880317408824</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.2202246038128996</v>
+        <v>0.0601697899069786</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1312</v>
+        <v>1454</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>台富</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>446.2769482013298</v>
+        <v>588.1650806538985</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>12.85</v>
+        <v>12.95</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>53.84968083943214</v>
+        <v>48.88999471764837</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>33.56913331206421</v>
+        <v>26.54661263155507</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.6276948201329806</v>
+        <v>0.3165080653898401</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.2303487438846832</v>
+        <v>0.0230484203994732</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1437</v>
+        <v>1537</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>廣隆</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>446.0482961949619</v>
+        <v>583.5488446582</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>29.15</v>
+        <v>127.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>55.18528180935385</v>
+        <v>60.18179811415604</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>27.79078432157316</v>
+        <v>12.80726886527522</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.604829619496188</v>
+        <v>0.8548844658200014</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.1263892463198902</v>
+        <v>0.0437853666520038</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1537</v>
+        <v>1341</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>廣隆</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>443.3439329425922</v>
+        <v>582.5123827747382</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>127.5</v>
+        <v>62.1</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>60.18179820674028</v>
+        <v>52.00754733569675</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>12.80726885338719</v>
+        <v>13.71275845174855</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.8343932942592251</v>
+        <v>0.7512382774738142</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0437853666520038</v>
+        <v>-0.0438292752200797</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1504</v>
+        <v>1110</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>439.0947383078257</v>
+        <v>575.0250163061588</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>68.40000000000001</v>
+        <v>15.4</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>44.52192688682394</v>
+        <v>57.33795087227513</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>28.0933519912833</v>
+        <v>28.74518618519308</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4094738307825665</v>
+        <v>0.5025016306158837</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-1.014865539885452</v>
+        <v>0.1283582524010316</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1256</v>
+        <v>1417</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>438.5054366642113</v>
+        <v>573.0366597273166</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>175</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>43.36890865939573</v>
+        <v>51.39742218245775</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>30.20475279841633</v>
+        <v>24.15270031240957</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.8505436664211358</v>
+        <v>0.803665972731665</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,11 +3114,11 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-3.669076577714482</v>
+        <v>0.0511573061887445</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>431.728366458287</v>
+        <v>571.8077371974731</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>21.3</v>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>51.44187179751401</v>
+        <v>51.44187176576122</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>17.39525836569008</v>
+        <v>17.39525848703298</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.672836645828698</v>
+        <v>1.68077371974731</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0293183280131029</v>
+        <v>0.0293183280226453</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1110</v>
+        <v>1475</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>東泥</t>
+          <t>業旺</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>429.9799246786392</v>
+        <v>569.7665652474806</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>15.4</v>
+        <v>27</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>57.33795095168251</v>
+        <v>57.97881733840253</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>28.74518623583413</v>
+        <v>30.97600493351099</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4979924678639235</v>
+        <v>0.4766565247480559</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.1283582524010316</v>
+        <v>0.3262456827953323</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1418</v>
+        <v>1453</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>429.4458840198619</v>
+        <v>565.0187576623473</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>18.7</v>
+        <v>11.55</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>52.06451544664237</v>
+        <v>52.00653104874696</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>22.11948976392872</v>
+        <v>20.61665208384618</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.9445884019861884</v>
+        <v>1.501875766234722</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0472081453261307</v>
+        <v>0.0568063672489621</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1449</v>
+        <v>1436</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>佳和</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>425.0814328623795</v>
+        <v>563.9809517805829</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>14.25</v>
+        <v>45.8</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>54.54497652700282</v>
+        <v>44.77447226931574</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>22.66745204364586</v>
+        <v>34.65924666463019</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.008143286237949</v>
+        <v>1.3980951780583</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.2291860643935573</v>
+        <v>0.3853708530665445</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1417</v>
+        <v>1447</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>422.9212788112513</v>
+        <v>557.0728586705641</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>6.22</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>51.39742228358032</v>
+        <v>54.84532876128607</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>24.15270020354106</v>
+        <v>40.52526249518368</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.7921278811251288</v>
+        <v>0.7072858670563997</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0511573061772972</v>
+        <v>0.0084421362843605</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1432</v>
+        <v>1459</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>418.5661934103305</v>
+        <v>555.4158835814468</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>17.2</v>
+        <v>11.8</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>58.80003280026887</v>
+        <v>54.07474203727521</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>24.28996831641306</v>
+        <v>21.61276081116337</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.8566193410330448</v>
+        <v>0.5415883581446785</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.1036999382413324</v>
+        <v>0.0052608265533633</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, above_ema60, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1460</v>
+        <v>1215</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>宏遠</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>412.5532620150212</v>
+        <v>554.8498382703241</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>7.09</v>
+        <v>117.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>50.45564681291501</v>
+        <v>32.30016008282591</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>18.49857941277646</v>
+        <v>40.16370955819798</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.7553262015021172</v>
+        <v>0.9849838270324084</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.0064018561248133</v>
+        <v>-0.9268021159591244</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1234</v>
+        <v>1465</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>黑松</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>411.6824303120125</v>
+        <v>552.2871782640959</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>35.2</v>
+        <v>12.4</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>57.76457931642747</v>
+        <v>53.97228938734305</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>19.00320199443733</v>
+        <v>19.62128519371332</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.168243031201252</v>
+        <v>0.7287178264095876</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.1311432493971228</v>
+        <v>0.0106467066544451</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1470</v>
+        <v>1301</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>大統新創</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>411.5228291119241</v>
+        <v>550.4984127812752</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>22.7</v>
+        <v>43.8</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,49 +3573,49 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>53.39648948284227</v>
+        <v>37.02724689055361</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>2.887508889762842</v>
+        <v>22.45878039693756</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.1522829111924132</v>
+        <v>1.049841278127511</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M59" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0184093528701427</v>
+        <v>-0.3196710935812031</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1304</v>
+        <v>1560</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>410.0376671382158</v>
+        <v>540.4815287335989</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>12.5</v>
+        <v>628</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,49 +3626,49 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>44.06401288604839</v>
+        <v>45.89935180549875</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>20.30791063309507</v>
+        <v>29.25591495450787</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.5037667138215798</v>
+        <v>1.04815287335989</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0638202153568472</v>
+        <v>-16.33365797506831</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>400.067915481897</v>
+        <v>529.5083753686196</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>65</v>
+        <v>18.7</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>50.83621209187815</v>
+        <v>52.06451546394356</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>19.33548358490197</v>
+        <v>22.11949005387031</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.5067915481897037</v>
+        <v>0.950837536861958</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.0734755862229159</v>
+        <v>0.0472081452116564</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1475</v>
+        <v>1503</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>業旺</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>399.7505743690131</v>
+        <v>524.9316685974968</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>27</v>
+        <v>215</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>57.97881717736355</v>
+        <v>50.06895430446874</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>30.97600497302929</v>
+        <v>26.6144781086898</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.475057436901315</v>
+        <v>0.4931668597496888</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.3262456828907288</v>
+        <v>-0.5787878608237378</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1582</v>
+        <v>1524</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>392.847373948955</v>
+        <v>522.7877233149707</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>89.2</v>
+        <v>29.75</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>36.60712686286187</v>
+        <v>46.1734023627781</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>26.31482193144292</v>
+        <v>21.49374207805894</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.2847373948955035</v>
+        <v>0.278772331497062</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-3.28890369810283</v>
+        <v>-0.2224029814300434</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1454</v>
+        <v>1517</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>台富</t>
+          <t>利奇</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>387.6263811631168</v>
+        <v>522.043013277671</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>12.95</v>
+        <v>10.25</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>48.88999464891873</v>
+        <v>48.4608165537358</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>26.54661259842011</v>
+        <v>23.55339908816925</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.2626381163116774</v>
+        <v>0.7043013277671049</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.0230484204185528</v>
+        <v>0.0354866766275143</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1459</v>
+        <v>1229</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>385.2313321221056</v>
+        <v>514.1175224501424</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>11.8</v>
+        <v>41.3</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>54.07474220393636</v>
+        <v>50.47040396603869</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>21.61276081116337</v>
+        <v>28.03704247745851</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.523133212210557</v>
+        <v>0.4117522450142343</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0052608265724427</v>
+        <v>0.2201962713413369</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1313</v>
+        <v>1466</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>380.5093670301065</v>
+        <v>509.2091254769391</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>11.05</v>
+        <v>14.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>50.0370874058077</v>
+        <v>45.60848549968438</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>17.76456413889047</v>
+        <v>21.33985152430927</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5509367030106478</v>
+        <v>0.9209125476939124</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.060169789872636</v>
+        <v>0.0854376161024461</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>379.4152917594202</v>
+        <v>508.2222902528947</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>25.2</v>
+        <v>23.15</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>44.26794334377355</v>
+        <v>54.34604702270502</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>12.16902551596889</v>
+        <v>20.5473743071575</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.4415291759420178</v>
+        <v>0.8222290252894644</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.1896923874829083</v>
+        <v>0.1248952950893959</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1517</v>
+        <v>1419</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>利奇</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>376.9373827093148</v>
+        <v>500.1502900372032</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>10.25</v>
+        <v>65</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>48.46081665493519</v>
+        <v>50.83621212010239</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>23.55339903768305</v>
+        <v>19.33548356811996</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.693738270931477</v>
+        <v>0.515029003720313</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0354866766275143</v>
+        <v>-0.0734755862515261</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1101</v>
+        <v>1314</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>369.5900446853882</v>
+        <v>500.0664855856904</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>24.25</v>
+        <v>7.76</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>49.09168118564746</v>
+        <v>55.68662176485324</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>11.7216656766396</v>
+        <v>14.48892079873993</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.9590044685388192</v>
+        <v>0.5066485585690443</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.0161292668860622</v>
+        <v>0.072795379082279</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1229</v>
+        <v>1316</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>369.0191700817398</v>
+        <v>494.314273066847</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>41.3</v>
+        <v>10.8</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>50.47040405878517</v>
+        <v>50.85066449531143</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>28.03704245051808</v>
+        <v>19.61641181350405</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.4019170081739765</v>
+        <v>2.931427306684701</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.2201962713222519</v>
+        <v>0.1070552469055858</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1316</v>
+        <v>1506</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>正道</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>364.2597943249651</v>
+        <v>492.6015741735621</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>10.8</v>
+        <v>10.2</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>50.8506646794771</v>
+        <v>46.83870606400379</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>19.61641181506551</v>
+        <v>21.17879798553386</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>2.925979432496513</v>
+        <v>0.7601574173562099</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.1070552469151255</v>
+        <v>0.0186923287975502</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1529</v>
+        <v>1452</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>宏益</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>363.1479244962227</v>
+        <v>492.242317003423</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>23.15</v>
+        <v>10.95</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>54.34604705652693</v>
+        <v>52.37093324033624</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>20.54737426048289</v>
+        <v>22.67453926334595</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.8147924496222725</v>
+        <v>0.2242317003422967</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.1248952951466378</v>
+        <v>0.0702355899791615</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1217</v>
+        <v>1233</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>天仁</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>362.645848833149</v>
+        <v>491.2005520564346</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>9.859999999999999</v>
+        <v>28</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>54.30369379821217</v>
+        <v>46.26759940919055</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>27.19751940342042</v>
+        <v>24.31689807494447</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.7645848833149033</v>
+        <v>0.1200552056434603</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0402647761118265</v>
+        <v>0.0188467847902318</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1452</v>
+        <v>1217</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>362.1090412681857</v>
+        <v>482.7474317772203</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>10.95</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>52.3709334256375</v>
+        <v>54.30369363065711</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>22.67453917198063</v>
+        <v>27.19751955410407</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.2109041268185687</v>
+        <v>0.7747431777220285</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.07023558996962161</v>
+        <v>0.0402647761404463</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1219</v>
+        <v>1201</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>358.3622821364543</v>
+        <v>480.818543140979</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>37.8375172309057</v>
+        <v>50.73708514676647</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>33.9240132784874</v>
+        <v>32.70581211899528</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.3362282136454289</v>
+        <v>0.5818543140979011</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0245216319138984</v>
+        <v>0.0599767952080931</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1440</v>
+        <v>1474</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>弘裕</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>355.3541700176065</v>
+        <v>479.2675293302772</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>13.1</v>
+        <v>10.1</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>51.77282749206287</v>
+        <v>50.5918335812294</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>28.79225875194092</v>
+        <v>28.75524498876055</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.5354170017606529</v>
+        <v>0.4267529330277216</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0596224747412226</v>
+        <v>0.0277577426787508</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1453</v>
+        <v>1504</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>354.3664724482231</v>
+        <v>479.1518590493268</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>11.55</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,49 +4527,49 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>52.00653111329901</v>
+        <v>44.52192688215824</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>20.61665205918188</v>
+        <v>28.09335200631316</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.43664724482231</v>
+        <v>0.4151859049326777</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M77" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0568063672871201</v>
+        <v>-1.014865540038092</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1465</v>
+        <v>1102</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>352.0316131034968</v>
+        <v>471.5948014129308</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>12.4</v>
+        <v>34.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>53.97228943993647</v>
+        <v>52.30402260552109</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>19.62128521094997</v>
+        <v>12.14274748478256</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.703161310349677</v>
+        <v>0.6594801412930792</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0106467066639856</v>
+        <v>0.1106758082215454</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1305</v>
+        <v>1522</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>351.8655316860572</v>
+        <v>464.711146995235</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>12.65</v>
+        <v>30.9</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>44.98730758310413</v>
+        <v>47.27659383700256</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>14.2886760951415</v>
+        <v>21.65021168827932</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.6865531686057227</v>
+        <v>0.471114699523497</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0757271455881373</v>
+        <v>0.0266910574379332</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1308</v>
+        <v>1337</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>再生-KY</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>341.201463409637</v>
+        <v>464.0797639253768</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>13.45</v>
+        <v>4.97</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>45.26514026750607</v>
+        <v>48.12832957434221</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>16.20769051836289</v>
+        <v>22.52141990229793</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.6201463409636971</v>
+        <v>0.4079763925376821</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0831935848051672</v>
+        <v>0.033946449546396</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1233</v>
+        <v>1324</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>天仁</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>341.0978521742047</v>
+        <v>463.7987563847813</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>28</v>
+        <v>10.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>46.26759944821803</v>
+        <v>50.65305299861099</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>24.31689790472937</v>
+        <v>22.23646699396658</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.1097852174204743</v>
+        <v>0.3798756384781295</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0188467847902318</v>
+        <v>0.0413100778876455</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1201</v>
+        <v>1219</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>340.7386086637676</v>
+        <v>453.4355899825962</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>50.73708516988773</v>
+        <v>37.8375172309057</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>32.70581214240426</v>
+        <v>33.9240132784874</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.5738608663767614</v>
+        <v>0.3435589982596226</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0599767952176352</v>
+        <v>0.0245216319043588</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1474</v>
+        <v>1413</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>弘裕</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>339.1030150730689</v>
+        <v>452.2111295193667</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>10.1</v>
+        <v>9.51</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>50.5918337917624</v>
+        <v>51.10607216877482</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>28.75524449652905</v>
+        <v>5.687477337632785</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.4103015073068881</v>
+        <v>0.7211129519366704</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.0277577426310528</v>
+        <v>0.0029536129916187</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1457</v>
+        <v>1312</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>宜進</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>325.593493444182</v>
+        <v>446.3049821827812</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>14.35</v>
+        <v>12.85</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>46.85017088129391</v>
+        <v>53.84968078281594</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>22.20200753410468</v>
+        <v>33.56913335233477</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.5593493444181984</v>
+        <v>0.6304982182781186</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.06578706853344959</v>
+        <v>0.2303487439896197</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>1436</v>
+        <v>1326</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>318.7017761527791</v>
+        <v>444.9785812557291</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>45.8</v>
+        <v>46.25</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>44.77447262157295</v>
+        <v>43.32272499225733</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>34.65924648171765</v>
+        <v>23.71817627554806</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.370177615277915</v>
+        <v>0.4978581255729093</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.3853708529711501</v>
+        <v>-0.3475507867642392</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1220</v>
+        <v>1527</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>鑽全</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>318.349101958275</v>
+        <v>444.5478179289959</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>11.6</v>
+        <v>33.15</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>30.85019322871086</v>
+        <v>53.63660429211782</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>30.69364911739316</v>
+        <v>18.97046278613698</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.834910195827502</v>
+        <v>0.9547817928995928</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0062166461957643</v>
+        <v>0.012158001554431</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1413</v>
+        <v>1460</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>宏遠</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>311.830124412201</v>
+        <v>442.6094763688319</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>9.51</v>
+        <v>7.09</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>51.10607214435766</v>
+        <v>50.45564681291501</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>5.687477336687191</v>
+        <v>18.49857941277646</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.6830124412200979</v>
+        <v>0.760947636883186</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0029536130202384</v>
+        <v>-0.0064018561248133</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1519</v>
+        <v>1340</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>309.9875386021641</v>
+        <v>440.5433646746939</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>773</v>
+        <v>5.63</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>39.76022474736378</v>
+        <v>48.2983657011439</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>12.84786524259517</v>
+        <v>20.49104340255754</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.9987538602164124</v>
+        <v>0.5543364674693863</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-7.44734197205161</v>
+        <v>0.0377729960666993</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1466</v>
+        <v>1539</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>巨庭</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>309.0550924011232</v>
+        <v>440.4279249038693</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>14.5</v>
+        <v>15.7</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>45.60848532779456</v>
+        <v>43.42194000491806</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>21.3398515059515</v>
+        <v>23.24931883234201</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.905509240112318</v>
+        <v>0.5427924903869276</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0854376161406053</v>
+        <v>-0.0230949533383438</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1102</v>
+        <v>1323</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>301.5809948629875</v>
+        <v>424.7886480424201</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>34.5</v>
+        <v>19.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>52.30402255961684</v>
+        <v>41.08413343900699</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>12.14274753928425</v>
+        <v>11.87214901944325</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.6580994862987508</v>
+        <v>0.4788648042420116</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.1106758082215454</v>
+        <v>-0.0636634650199104</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1476</v>
+        <v>1416</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>300.9293438713187</v>
+        <v>422.4875172256684</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>344</v>
+        <v>11.05</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>49.80689501980611</v>
+        <v>42.11014220369474</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>13.81206432607695</v>
+        <v>32.21203698107721</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.592934387131866</v>
+        <v>0.7487517225668393</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.10769900308772</v>
+        <v>-0.0227416484354094</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1536</v>
+        <v>1108</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>299.8724296308855</v>
+        <v>421.8439429133954</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>48.55</v>
+        <v>13.65</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>41.52941364877136</v>
+        <v>40.6301479903659</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>13.43917984272093</v>
+        <v>42.70165700569322</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.4872429630885501</v>
+        <v>0.6843942913395372</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.3156533661319371</v>
+        <v>0.0277635811481215</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1526</v>
+        <v>1220</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>日馳</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>298.6161774498353</v>
+        <v>420.3186281565218</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>14.25</v>
+        <v>11.6</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>35.94033255728858</v>
+        <v>30.85019313123536</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>23.37931335711012</v>
+        <v>30.69364917239213</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.861617744983536</v>
+        <v>1.031862815652183</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0392637406628768</v>
+        <v>0.0062166462053036</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1540</v>
+        <v>1308</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>喬福</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>295.4754042352931</v>
+        <v>416.2413149103201</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>21.55</v>
+        <v>13.45</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>48.49971874819601</v>
+        <v>45.26514025009732</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>22.37741331844526</v>
+        <v>16.20769049473612</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.5475404235293053</v>
+        <v>0.6241314910320126</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0054759809948073</v>
+        <v>0.0831935847860885</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1340</v>
+        <v>1476</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>295.4118431612447</v>
+        <v>416.0111576921195</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>5.63</v>
+        <v>344</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,49 +5481,49 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>48.29836573564938</v>
+        <v>49.80689498524658</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>20.49104340676015</v>
+        <v>13.8120643169411</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.5411843161244729</v>
+        <v>0.6011157692119472</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0377729960800557</v>
+        <v>0.1076990019429477</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>巨庭</t>
+          <t>喬福</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>295.3870316696763</v>
+        <v>415.4919074961426</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>15.7</v>
+        <v>21.55</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>43.42194022428586</v>
+        <v>48.49971864084133</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>23.24931871039712</v>
+        <v>22.37741333898225</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.5387031669676323</v>
+        <v>0.5491907496142656</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0230949533860438</v>
+        <v>0.0054759810138868</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1515</v>
+        <v>1536</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>力山</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>294.0961615495603</v>
+        <v>414.9710080434382</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>22.9</v>
+        <v>48.55</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>48.84366266283243</v>
+        <v>41.52941352330599</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>20.22203143961032</v>
+        <v>13.43917984272093</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.409616154956037</v>
+        <v>0.4971008043438215</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.1051692055463605</v>
+        <v>-0.3156533661319371</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>1337</v>
+        <v>1231</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>再生-KY</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>294.0364036933643</v>
+        <v>410.951000703492</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>4.97</v>
+        <v>87.2</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>48.12832982465856</v>
+        <v>51.85424962173578</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>22.52141966299546</v>
+        <v>17.78242752350376</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.4036403693364296</v>
+        <v>0.5951000703491932</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.033946449515869</v>
+        <v>0.2630110530290138</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1324</v>
+        <v>1256</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>293.6880244258975</v>
+        <v>398.7721891598398</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>10.5</v>
+        <v>175</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>50.65305305729768</v>
+        <v>43.36890861731651</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>22.23646699237445</v>
+        <v>30.2047524410071</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.3688024425897531</v>
+        <v>0.8772189159839808</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0413100778971869</v>
+        <v>-3.669076577714482</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1439</v>
+        <v>1582</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>289.2966947277964</v>
+        <v>392.893776854972</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>25.15</v>
+        <v>89.2</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>48.71818352068126</v>
+        <v>36.60712685048471</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>4.57840634370066</v>
+        <v>26.31482193144292</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.4296694727796432</v>
+        <v>0.2893776854972049</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.0410847723510172</v>
+        <v>-3.288903698160078</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>1309</v>
+        <v>1445</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>284.3455053309951</v>
+        <v>390.1510321092281</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>15.15</v>
+        <v>11.25</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>41.17410698429823</v>
+        <v>35.11721795866272</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>12.78942468226558</v>
+        <v>11.22603319286937</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.4345505330995061</v>
+        <v>0.5151032109228109</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0184362292669579</v>
+        <v>-0.002013794982548</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>1506</v>
+        <v>1439</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>282.5761583661767</v>
+        <v>389.3640974122921</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>10.2</v>
+        <v>25.15</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>46.83870614879513</v>
+        <v>48.71818353738647</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>21.17879785634712</v>
+        <v>4.578406375291363</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.7576158366176767</v>
+        <v>0.4364097412292109</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0186923287975502</v>
+        <v>-0.0410847724082558</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>1338</v>
+        <v>1440</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>279.9957172476973</v>
+        <v>385.3879863870898</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>16.45</v>
+        <v>13.1</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>51.39456373342988</v>
+        <v>51.77282747249949</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>19.89696955474245</v>
+        <v>28.79225876271926</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.4995717247697255</v>
+        <v>0.5387986387089801</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.0531340276597423</v>
+        <v>0.0596224747507628</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1215</v>
+        <v>1442</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>274.7644750202577</v>
+        <v>385.3528650441865</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>117.5</v>
+        <v>26.9</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>32.30016009846533</v>
+        <v>50.53219887814176</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>40.16370955133237</v>
+        <v>16.23629890125395</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.976447502025771</v>
+        <v>1.035286504418652</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.9268021159972806</v>
+        <v>0.1278302693290595</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1464</v>
+        <v>1225</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>270.6461557502826</v>
+        <v>385.1471494645858</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>10.3</v>
+        <v>29.35</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>50.30569584705533</v>
+        <v>42.34386218251622</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>22.82010462188357</v>
+        <v>14.41907181500585</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.5646155750282619</v>
+        <v>1.014714946458582</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,51 +6029,51 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.0129521148213219</v>
+        <v>0.1330985999103542</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1435</v>
+        <v>1103</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>中福</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>270</v>
+        <v>382.1218517641818</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>5.39</v>
+        <v>13.45</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G106" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>44.36127059952162</v>
+        <v>52.75365844919568</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>8.048357062981447</v>
+        <v>15.57912092304554</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>8.058882292826878</v>
+        <v>0.7121851764181772</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.1879611011394713</v>
+        <v>0.0337744004707353</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1310</v>
+        <v>1538</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>269.7699356375685</v>
+        <v>381.0351083652055</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>8.43</v>
+        <v>11.8</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>45.48705530183123</v>
+        <v>51.72657181113914</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>24.89791563685212</v>
+        <v>6.257243107236699</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.476993563756851</v>
+        <v>1.103510836520545</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0930682683053046</v>
+        <v>-0.2382185351745862</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>1225</v>
+        <v>1472</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>264.9857549701577</v>
+        <v>377.2144112595128</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>29.35</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>42.34386218251622</v>
+        <v>50.15888502996366</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>14.41907181500585</v>
+        <v>11.61719931892863</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.9985754970157704</v>
+        <v>1.721441125951274</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.1330985999103542</v>
+        <v>0.5981107842777845</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>1231</v>
+        <v>1304</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>260.5751212910028</v>
+        <v>370.0654416528378</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>87.2</v>
+        <v>12.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>51.85425015626764</v>
+        <v>44.06401285554033</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>17.78242722825869</v>
+        <v>20.30791056605971</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5575121291002834</v>
+        <v>0.5065441652837793</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.2630110522658442</v>
+        <v>0.063820215366387</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1323</v>
+        <v>1464</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>永裕</t>
+          <t>得力</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>254.7102157514325</v>
+        <v>365.7711123536067</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>19.5</v>
+        <v>10.3</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>41.08413347477376</v>
+        <v>50.30569549676851</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>11.87214912278679</v>
+        <v>22.82010464797339</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.4710215751432494</v>
+        <v>0.5771112353606658</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0636634650485307</v>
+        <v>0.0129521148403997</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>1521</v>
+        <v>1338</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>253.998315603214</v>
+        <v>355.0127801430007</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>25.9</v>
+        <v>16.45</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>48.72476906965781</v>
+        <v>51.39456375182171</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>19.56578702303995</v>
+        <v>19.89696957748192</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.3998315603213965</v>
+        <v>0.5012780143000646</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.1107184781614515</v>
+        <v>0.0531340276025035</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>1108</v>
+        <v>1528</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>251.7909590022529</v>
+        <v>344.4570125219684</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>13.65</v>
+        <v>25.2</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>40.6301479903659</v>
+        <v>44.26794331842621</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>42.70165702302336</v>
+        <v>12.16902549378628</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.67909590022529</v>
+        <v>0.4457012521968417</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0277635811576605</v>
+        <v>-0.1896923874733673</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1472</v>
+        <v>1109</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>236.8258220282059</v>
+        <v>335.2926436256747</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>88.09999999999999</v>
+        <v>14.6</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>50.15888509958756</v>
+        <v>39.79241447820166</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>11.61719930808672</v>
+        <v>32.51364150629497</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.682582202820596</v>
+        <v>0.5292643625674651</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.5981107836099893</v>
+        <v>0.0241031106764441</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>1538</v>
+        <v>1526</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>日馳</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>231.0327919092859</v>
+        <v>328.6491517071167</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>11.8</v>
+        <v>14.25</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>51.72657180759585</v>
+        <v>35.94033229947877</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>6.25724310637363</v>
+        <v>23.37931348446757</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.103279190928593</v>
+        <v>0.864915170711672</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.2382185351745862</v>
+        <v>0.0392637407678122</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>1527</v>
+        <v>1457</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>宜進</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>229.4619454094429</v>
+        <v>325.6358075519162</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>33.15</v>
+        <v>14.35</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>53.63660457213551</v>
+        <v>46.85017086943418</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>18.97046278054706</v>
+        <v>22.20200747498663</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.946194540944287</v>
+        <v>0.5635807551916219</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0121580015162754</v>
+        <v>0.0657870685048306</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>1569</v>
+        <v>1515</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>229.1266543995035</v>
+        <v>324.1222415605137</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>47.55</v>
+        <v>22.9</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>34.95046786826941</v>
+        <v>48.84366243559602</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>13.17205651054173</v>
+        <v>20.2220316940561</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.912665439950349</v>
+        <v>0.4122241560513683</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.3307238413932518</v>
+        <v>0.1051692058897887</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>1535</v>
+        <v>1213</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>中宇</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>226.4795963988995</v>
+        <v>314.2360856898237</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>49.4</v>
+        <v>8.32</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>44.89371643559728</v>
+        <v>50.78414193125315</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>20.52073857795142</v>
+        <v>10.60126947573059</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.6479596398899505</v>
+        <v>0.4236085689823653</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.0373086016814697</v>
+        <v>0.1027552604679287</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>1445</v>
+        <v>1558</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>大宇</t>
+          <t>伸興</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>220.1217777992022</v>
+        <v>312.0555430902317</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>11.25</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>35.11721811016677</v>
+        <v>44.8530732070111</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>11.22603315885651</v>
+        <v>13.12185102694666</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.5121777799202207</v>
+        <v>0.7055543090231733</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0020137949253085</v>
+        <v>-0.0152352416524561</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>1442</v>
+        <v>1305</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>215.2603693858105</v>
+        <v>311.9396273133873</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>26.9</v>
+        <v>12.65</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>50.53219888829123</v>
+        <v>44.98730756965236</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>16.23629913558539</v>
+        <v>14.28867609358442</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.026036938581053</v>
+        <v>0.6939627313387288</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.1278302698823638</v>
+        <v>0.07572714556905739</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>1558</v>
+        <v>1463</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>伸興</t>
+          <t>強盛新</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>211.950405382394</v>
+        <v>309.0848780732427</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>90.40000000000001</v>
+        <v>17.65</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>44.85307331605426</v>
+        <v>42.84673104068202</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>13.12185104150477</v>
+        <v>10.11888344696222</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.6950405382393928</v>
+        <v>0.9084878073242768</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.0152352416524561</v>
+        <v>-0.0050480782001436</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>1103</v>
+        <v>1235</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>興泰</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>211.9354144147446</v>
+        <v>304.3593303389138</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>13.45</v>
+        <v>38</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>52.75365857847118</v>
+        <v>41.42796033147794</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>15.57912086328352</v>
+        <v>12.06205230438291</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.6935414414744638</v>
+        <v>0.4359330338913842</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.0337744004516565</v>
+        <v>-0.1239179160248742</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>1541</v>
+        <v>1315</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>錩泰</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>210.6539217846438</v>
+        <v>302.2856688336868</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>20.55</v>
+        <v>61.2</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>36.13116398714234</v>
+        <v>44.7117018303328</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>13.59686180470771</v>
+        <v>14.72393111466843</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.5653921784643782</v>
+        <v>0.228566883368677</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.056928230067483</v>
+        <v>0.037971696938693</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>1463</v>
+        <v>1519</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>208.7894242299313</v>
+        <v>290.7468640333558</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>17.65</v>
+        <v>773</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>42.84673136078097</v>
+        <v>39.76022474939459</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>10.11888329159775</v>
+        <v>12.8478652448506</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.8789424229931339</v>
+        <v>1.074686403335586</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.0050480782860034</v>
+        <v>-7.447341973768685</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>1235</v>
+        <v>1309</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>興泰</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>184.3556022572908</v>
+        <v>284.3678330487954</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>38</v>
+        <v>15.15</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>41.42796022790665</v>
+        <v>41.1741069355254</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>12.06205223551672</v>
+        <v>12.7894246469044</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.4355602257290869</v>
+        <v>0.4367833048795361</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.1239179160248742</v>
+        <v>0.0184362293051177</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>1512</v>
+        <v>1325</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>瑞利</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>172.2131659094803</v>
+        <v>280.7576052873513</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>6.86</v>
+        <v>26.05</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>44.03742224603462</v>
+        <v>42.20453173985155</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>11.48255190188673</v>
+        <v>14.00738775978631</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.7213165909480256</v>
+        <v>0.5757605287351317</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.0063347903091021</v>
+        <v>-0.0919407658354989</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>1109</v>
+        <v>1535</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>中宇</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>165.0741459578085</v>
+        <v>256.5348373221859</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>14.6</v>
+        <v>49.4</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>39.79241447820166</v>
+        <v>44.8937163622096</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>32.51364159146166</v>
+        <v>20.52073857795142</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.5074145957808476</v>
+        <v>0.6534837322185851</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.0241031106955204</v>
+        <v>0.0373086016433129</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>1473</v>
+        <v>1310</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>164.5095932041195</v>
+        <v>249.8279000226264</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>20.4</v>
+        <v>8.43</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>39.70863172770645</v>
+        <v>45.48705523103565</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>25.63159599676704</v>
+        <v>24.89791560187073</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.4509593204119475</v>
+        <v>0.4827900022626378</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.0578531539124378</v>
+        <v>0.0930682683186608</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>1410</v>
+        <v>1541</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>錩泰</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>138.7385366287679</v>
+        <v>240.7033559959136</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>24.9</v>
+        <v>20.55</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,16 +7230,16 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>32.34607815794622</v>
+        <v>36.13116403280066</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>12.18691258421733</v>
+        <v>13.59686182893698</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.8738536628767898</v>
+        <v>0.5703355995913586</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128" s="2" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.0091837110317058</v>
+        <v>0.0569282298766831</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>1325</v>
+        <v>1451</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>恆大</t>
+          <t>年興</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>135.7178629395696</v>
+        <v>236.1690631485325</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>26.05</v>
+        <v>16.5</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>42.2045317586872</v>
+        <v>40.22777141350822</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>14.00738777495304</v>
+        <v>14.06896234928934</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.5717862939569616</v>
+        <v>0.6169063148532463</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.09194076581641961</v>
+        <v>0.0179293813909385</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>1213</v>
+        <v>1435</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>134.2354934349852</v>
+        <v>235.744744632218</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>8.32</v>
+        <v>5.36</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,13 +7336,13 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>50.78414200727237</v>
+        <v>44.34023105610312</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>10.60126944264617</v>
+        <v>8.192646265935108</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.4235493434985176</v>
+        <v>1.574474463221793</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>0.1027552602866733</v>
+        <v>-0.3529364444291258</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>1315</v>
+        <v>1569</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>132.2727498710925</v>
+        <v>229.1266543995035</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>61.2</v>
+        <v>47.55</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,16 +7389,16 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>44.71170189726186</v>
+        <v>34.95046787271288</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>14.72393111099459</v>
+        <v>13.17205663442637</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.2272749871092468</v>
+        <v>1.912665439950349</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" s="2" t="n">
         <v>0</v>
@@ -7407,31 +7407,31 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>0.037971696862374</v>
+        <v>-0.3307238423853851</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>1471</v>
+        <v>1468</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>昶和</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>127.1440329797481</v>
+        <v>216.9132904228972</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>10.6</v>
+        <v>11.6</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,16 +7442,16 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>42.54225974876427</v>
+        <v>30.39008677532037</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>16.00602565714233</v>
+        <v>11.53139172388069</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.7144032979748094</v>
+        <v>1.191329042289717</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" s="2" t="n">
         <v>0</v>
@@ -7460,31 +7460,31 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>9.946244574898788e-06</v>
+        <v>-0.0428851843864655</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>1441</v>
+        <v>1521</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>115.0490484456198</v>
+        <v>214.0144880196531</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>9.1</v>
+        <v>25.9</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7495,13 +7495,13 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>36.47503710506992</v>
+        <v>48.72476911354232</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>13.29568283677287</v>
+        <v>19.56578707563544</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.5049048445619836</v>
+        <v>0.4014488019653077</v>
       </c>
       <c r="K133" s="2" t="n">
         <v>0</v>
@@ -7513,31 +7513,31 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>0.0041724720367306</v>
+        <v>-0.1107184781996124</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>1451</v>
+        <v>1441</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>年興</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>96.11639613043418</v>
+        <v>211.4543225779012</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>16.5</v>
+        <v>9.1</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -7548,16 +7548,16 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>40.22777126672165</v>
+        <v>36.47503713317001</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>14.06896231232229</v>
+        <v>13.2956828334102</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.6116396130434186</v>
+        <v>0.6454322577901187</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134" s="2" t="n">
         <v>0</v>
@@ -7566,31 +7566,31 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>0.0179293814481759</v>
+        <v>0.0041724720176514</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>1468</v>
+        <v>1473</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>昶和</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>71.78747188196812</v>
+        <v>194.8020942048757</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>11.6</v>
+        <v>20.4</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -7601,16 +7601,16 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>30.39008683359127</v>
+        <v>39.70863154767365</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>11.53139165951516</v>
+        <v>25.63159613960831</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>1.178747188196812</v>
+        <v>0.4802094204875666</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L135" s="2" t="n">
         <v>0</v>
@@ -7619,9 +7619,168 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>-0.0428851843960059</v>
+        <v>0.0578531539792171</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>1512</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>瑞利</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>172.4338979135137</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>44.03742220717348</v>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>11.48255193749648</v>
+      </c>
+      <c r="J136" s="2" t="n">
+        <v>0.7433897913513704</v>
+      </c>
+      <c r="K136" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N136" s="2" t="n">
+        <v>0.0063347903224577</v>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>1471</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>首利</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>157.1638810896792</v>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>42.54225969636994</v>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>16.00602573616442</v>
+      </c>
+      <c r="J137" s="2" t="n">
+        <v>0.7163881089679157</v>
+      </c>
+      <c r="K137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N137" s="2" t="n">
+        <v>9.946229311746936e-06</v>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>南染</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>98.7385366287679</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>32.34607807326709</v>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>12.18691259250295</v>
+      </c>
+      <c r="J138" s="2" t="n">
+        <v>0.8738536628767898</v>
+      </c>
+      <c r="K138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N138" s="2" t="n">
+        <v>0.009183711117562899</v>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
